--- a/test/fixtures/Config_Combined.xlsx
+++ b/test/fixtures/Config_Combined.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DHL.ITS.RPAForge.SAP.SapConfig</t>
+          <t>CPMForge.SAP.SapConfig</t>
         </is>
       </c>
     </row>
